--- a/labeled/Add_Eating/July/multi_seed_results/seed_404/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_404/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1162 +442,746 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58.76591491699219</v>
+        <v>9.027777671813965</v>
       </c>
       <c r="B2" t="n">
-        <v>59.72500228881836</v>
+        <v>11.02173042297363</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54.29999923706055</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="B3" t="n">
-        <v>53.59627532958984</v>
+        <v>34.05576705932617</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100</v>
+        <v>54.66666793823242</v>
       </c>
       <c r="B4" t="n">
-        <v>89.51604461669922</v>
+        <v>56.05821228027344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>42.90000152587891</v>
+        <v>22.13516235351562</v>
       </c>
       <c r="B5" t="n">
-        <v>44.29942321777344</v>
+        <v>18.78845024108887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>12.30158710479736</v>
       </c>
       <c r="B6" t="n">
-        <v>23.29976272583008</v>
+        <v>9.311563491821289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>46.20000076293945</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B7" t="n">
-        <v>39.10535049438477</v>
+        <v>25.68874740600586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13.29365062713623</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="B8" t="n">
-        <v>9.824481964111328</v>
+        <v>31.78439331054688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36.23898315429688</v>
+        <v>6.502462863922119</v>
       </c>
       <c r="B9" t="n">
-        <v>40.65857315063477</v>
+        <v>6.141663074493408</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23.10000038146973</v>
+        <v>26.40394020080566</v>
       </c>
       <c r="B10" t="n">
-        <v>21.67893028259277</v>
+        <v>14.9151496887207</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22.6248779296875</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B11" t="n">
-        <v>20.86044311523438</v>
+        <v>16.05352783203125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53.20000076293945</v>
+        <v>92.90000152587891</v>
       </c>
       <c r="B12" t="n">
-        <v>45.30012893676758</v>
+        <v>67.46317291259766</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9.06403923034668</v>
+        <v>55.29999923706055</v>
       </c>
       <c r="B13" t="n">
-        <v>8.091938018798828</v>
+        <v>54.72276306152344</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2.938295841217041</v>
+        <v>10.47430801391602</v>
       </c>
       <c r="B14" t="n">
-        <v>9.179995536804199</v>
+        <v>12.87838745117188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>40</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="B15" t="n">
-        <v>37.60230255126953</v>
+        <v>93.18022918701172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>59.52381134033203</v>
+        <v>160.1999969482422</v>
       </c>
       <c r="B16" t="n">
-        <v>52.40569686889648</v>
+        <v>171.3939666748047</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>30.09523773193359</v>
+        <v>62.09523773193359</v>
       </c>
       <c r="B17" t="n">
-        <v>27.4379825592041</v>
+        <v>59.33684158325195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24.87757110595703</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="B18" t="n">
-        <v>24.69067764282227</v>
+        <v>13.29407215118408</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>28</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B19" t="n">
-        <v>23.14406776428223</v>
+        <v>19.16591644287109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19.84127044677734</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="B20" t="n">
-        <v>29.68650436401367</v>
+        <v>52.13379669189453</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>24.38785552978516</v>
       </c>
       <c r="B21" t="n">
-        <v>19.1748046875</v>
+        <v>22.13032531738281</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13.29365062713623</v>
+        <v>28.5</v>
       </c>
       <c r="B22" t="n">
-        <v>9.824481964111328</v>
+        <v>29.79849433898926</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35.5</v>
+        <v>11.43984222412109</v>
       </c>
       <c r="B23" t="n">
-        <v>28.93226432800293</v>
+        <v>12.60357761383057</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>60</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B24" t="n">
-        <v>60.46028518676758</v>
+        <v>13.97354030609131</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>44.46620941162109</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="B25" t="n">
-        <v>44.50424575805664</v>
+        <v>54.03823852539062</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3.428011655807495</v>
+        <v>13.22233104705811</v>
       </c>
       <c r="B26" t="n">
-        <v>9.319760322570801</v>
+        <v>17.9824390411377</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7.783251285552979</v>
+        <v>21.5475025177002</v>
       </c>
       <c r="B27" t="n">
-        <v>7.136451721191406</v>
+        <v>19.02046585083008</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6.502462863922119</v>
+        <v>22.51984214782715</v>
       </c>
       <c r="B28" t="n">
-        <v>5.951592445373535</v>
+        <v>28.78845024108887</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>25.39682579040527</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="B29" t="n">
-        <v>18.39719772338867</v>
+        <v>14.29285049438477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6.502462863922119</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B30" t="n">
-        <v>5.498184204101562</v>
+        <v>12.77575397491455</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>19.64285659790039</v>
+        <v>40.59999847412109</v>
       </c>
       <c r="B31" t="n">
-        <v>18.59560203552246</v>
+        <v>35.07613754272461</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>10.7737512588501</v>
+        <v>15.0476188659668</v>
       </c>
       <c r="B32" t="n">
-        <v>16.68436622619629</v>
+        <v>22.5474853515625</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>51.59999847412109</v>
+        <v>13.71204662322998</v>
       </c>
       <c r="B33" t="n">
-        <v>41.90285873413086</v>
+        <v>20.64206886291504</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>44.70000076293945</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B34" t="n">
-        <v>42.63383865356445</v>
+        <v>26.39973831176758</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>28.7952995300293</v>
+        <v>60</v>
       </c>
       <c r="B35" t="n">
-        <v>34.7370491027832</v>
+        <v>31.64817047119141</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6.660137176513672</v>
+        <v>33.63095092773438</v>
       </c>
       <c r="B36" t="n">
-        <v>6.096660137176514</v>
+        <v>27.9380989074707</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8.275861740112305</v>
+        <v>24.87757110595703</v>
       </c>
       <c r="B37" t="n">
-        <v>9.329148292541504</v>
+        <v>24.25947761535645</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.665034294128418</v>
+        <v>5.221674919128418</v>
       </c>
       <c r="B38" t="n">
-        <v>8.007967948913574</v>
+        <v>7.814216136932373</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>37.59999847412109</v>
+        <v>40.25465393066406</v>
       </c>
       <c r="B39" t="n">
-        <v>32.03678131103516</v>
+        <v>33.70414352416992</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>30.15872955322266</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="B40" t="n">
-        <v>18.84202575683594</v>
+        <v>14.97391605377197</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11.11111068725586</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="B41" t="n">
-        <v>11.09983825683594</v>
+        <v>17.60431098937988</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>12.54940700531006</v>
+        <v>4.926108360290527</v>
       </c>
       <c r="B42" t="n">
-        <v>13.62323093414307</v>
+        <v>9.750758171081543</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>19.39275169372559</v>
+        <v>9.142857551574707</v>
       </c>
       <c r="B43" t="n">
-        <v>18.88240432739258</v>
+        <v>17.6037540435791</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17.10000038146973</v>
+        <v>20.37218475341797</v>
       </c>
       <c r="B44" t="n">
-        <v>15.7660608291626</v>
+        <v>17.8590087890625</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3.428011655807495</v>
+        <v>8.380952835083008</v>
       </c>
       <c r="B45" t="n">
-        <v>9.319760322570801</v>
+        <v>19.24360275268555</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45.80952453613281</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="B46" t="n">
-        <v>45.75952529907227</v>
+        <v>11.6873836517334</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19.09892272949219</v>
+        <v>11</v>
       </c>
       <c r="B47" t="n">
-        <v>20.19857597351074</v>
+        <v>12.66801261901855</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10.77075099945068</v>
+        <v>26.05288887023926</v>
       </c>
       <c r="B48" t="n">
-        <v>10.84071445465088</v>
+        <v>26.53374099731445</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>19.58863830566406</v>
+        <v>22.9187068939209</v>
       </c>
       <c r="B49" t="n">
-        <v>27.0840892791748</v>
+        <v>17.95104026794434</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>78.35455322265625</v>
+        <v>18.4761905670166</v>
       </c>
       <c r="B50" t="n">
-        <v>75.14756774902344</v>
+        <v>16.28017044067383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15.51383399963379</v>
+        <v>1.762977480888367</v>
       </c>
       <c r="B51" t="n">
-        <v>19.56158065795898</v>
+        <v>9.25599479675293</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>33.39862823486328</v>
+        <v>45.52381134033203</v>
       </c>
       <c r="B52" t="n">
-        <v>34.01255416870117</v>
+        <v>34.21421813964844</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>15.08875751495361</v>
+        <v>27.23809432983398</v>
       </c>
       <c r="B53" t="n">
-        <v>13.31984329223633</v>
+        <v>19.72410011291504</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.762977480888367</v>
+        <v>9.304603576660156</v>
       </c>
       <c r="B54" t="n">
-        <v>7.571682453155518</v>
+        <v>15.42512035369873</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B55" t="n">
-        <v>80.01177978515625</v>
+        <v>31.14836120605469</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>80</v>
+        <v>21.74338912963867</v>
       </c>
       <c r="B56" t="n">
-        <v>75.18447113037109</v>
+        <v>23.95799827575684</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>19.84127044677734</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B57" t="n">
-        <v>19.81364822387695</v>
+        <v>13.25483417510986</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>21.82539749145508</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="B58" t="n">
-        <v>26.12395668029785</v>
+        <v>21.53726577758789</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>19.19686508178711</v>
+        <v>28.10000038146973</v>
       </c>
       <c r="B59" t="n">
-        <v>21.91962623596191</v>
+        <v>21.76182174682617</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>29.39999961853027</v>
+        <v>57.78648376464844</v>
       </c>
       <c r="B60" t="n">
-        <v>28.73062515258789</v>
+        <v>53.06013488769531</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>8.952381134033203</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="B61" t="n">
-        <v>7.623764514923096</v>
+        <v>17.60997772216797</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>68.5</v>
+        <v>18.75</v>
       </c>
       <c r="B62" t="n">
-        <v>64.77831268310547</v>
+        <v>18.78218078613281</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>9.027777671813965</v>
+        <v>30.85210609436035</v>
       </c>
       <c r="B63" t="n">
-        <v>7.446281433105469</v>
+        <v>19.54812431335449</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>54.66666793823242</v>
+        <v>14.58333301544189</v>
       </c>
       <c r="B64" t="n">
-        <v>49.6426887512207</v>
+        <v>9.644015312194824</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>9.486166000366211</v>
+        <v>13.22233104705811</v>
       </c>
       <c r="B65" t="n">
-        <v>7.474339962005615</v>
+        <v>11.49604606628418</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12.30158710479736</v>
+        <v>20.66601371765137</v>
       </c>
       <c r="B66" t="n">
-        <v>7.564009189605713</v>
+        <v>22.30367088317871</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>35.20000076293945</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="B67" t="n">
-        <v>32.26577377319336</v>
+        <v>22.77921295166016</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>25.5238094329834</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B68" t="n">
-        <v>22.99095344543457</v>
+        <v>19.42269897460938</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>26.05288887023926</v>
+        <v>44.79999923706055</v>
       </c>
       <c r="B69" t="n">
-        <v>26.41663932800293</v>
+        <v>38.58302688598633</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>92.90000152587891</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="B70" t="n">
-        <v>89.22576141357422</v>
+        <v>24.00618743896484</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>19.39275169372559</v>
+        <v>19.74206352233887</v>
       </c>
       <c r="B71" t="n">
-        <v>18.88240432739258</v>
+        <v>14.51617622375488</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>19.0476188659668</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="B72" t="n">
-        <v>28.31479835510254</v>
+        <v>34.32510375976562</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>55.29999923706055</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="B73" t="n">
-        <v>59.63766860961914</v>
+        <v>24.53961944580078</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>10.47430801391602</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B74" t="n">
-        <v>11.88494205474854</v>
+        <v>14.96134948730469</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>103.8000030517578</v>
+        <v>28</v>
       </c>
       <c r="B75" t="n">
-        <v>103.2940292358398</v>
+        <v>34.18157577514648</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>35.90000152587891</v>
+        <v>9.162561416625977</v>
       </c>
       <c r="B76" t="n">
-        <v>37.34645462036133</v>
+        <v>9.908123970031738</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>25.46523094177246</v>
+        <v>11.4285717010498</v>
       </c>
       <c r="B77" t="n">
-        <v>25.38484191894531</v>
+        <v>18.88285446166992</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>23</v>
+        <v>63.0476188659668</v>
       </c>
       <c r="B78" t="n">
-        <v>24.33526229858398</v>
+        <v>54.41928482055664</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>24.38785552978516</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B79" t="n">
-        <v>26.7870979309082</v>
+        <v>24.35752868652344</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>28.5</v>
+        <v>68.85713958740234</v>
       </c>
       <c r="B80" t="n">
-        <v>30.4097957611084</v>
+        <v>65.12906646728516</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>11.43984222412109</v>
+        <v>25.46523094177246</v>
       </c>
       <c r="B81" t="n">
-        <v>9.956891059875488</v>
+        <v>27.83073997497559</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>38.19047546386719</v>
+        <v>59</v>
       </c>
       <c r="B82" t="n">
-        <v>27.11579132080078</v>
+        <v>39.1884765625</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>99.20635223388672</v>
+        <v>33.5</v>
       </c>
       <c r="B83" t="n">
-        <v>98.48637390136719</v>
+        <v>34.05929183959961</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>9.402546882629395</v>
+        <v>34.02777862548828</v>
       </c>
       <c r="B84" t="n">
-        <v>7.397078514099121</v>
+        <v>36.60883712768555</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>12.5</v>
+        <v>80.69999694824219</v>
       </c>
       <c r="B85" t="n">
-        <v>11.88475894927979</v>
+        <v>78.69876098632812</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>13.22233104705811</v>
+        <v>9.189723014831543</v>
       </c>
       <c r="B86" t="n">
-        <v>20.01656913757324</v>
+        <v>11.13221549987793</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>21.5475025177002</v>
+        <v>15.083251953125</v>
       </c>
       <c r="B87" t="n">
-        <v>14.38970851898193</v>
+        <v>10.59846305847168</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>22.51984214782715</v>
+        <v>19.19686508178711</v>
       </c>
       <c r="B88" t="n">
-        <v>16.49722480773926</v>
+        <v>31.19335746765137</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>20.66601371765137</v>
+        <v>40</v>
       </c>
       <c r="B89" t="n">
-        <v>19.18043327331543</v>
+        <v>37.92043304443359</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>13.22233104705811</v>
+        <v>14.1304349899292</v>
       </c>
       <c r="B90" t="n">
-        <v>20.01656913757324</v>
+        <v>10.60348701477051</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>23.5238094329834</v>
+        <v>16.96428489685059</v>
       </c>
       <c r="B91" t="n">
-        <v>20.42697715759277</v>
+        <v>11.45615196228027</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>15.0476188659668</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="B92" t="n">
-        <v>14.12822151184082</v>
+        <v>23.43936920166016</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>40</v>
+        <v>1.665034294128418</v>
       </c>
       <c r="B93" t="n">
-        <v>49.59688568115234</v>
+        <v>9.886968612670898</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>19.84127044677734</v>
+        <v>20.27424049377441</v>
       </c>
       <c r="B94" t="n">
-        <v>19.81364822387695</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>33.63095092773438</v>
-      </c>
-      <c r="B95" t="n">
-        <v>30.5615406036377</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>5.221674919128418</v>
-      </c>
-      <c r="B96" t="n">
-        <v>5.119080066680908</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>36.29999923706055</v>
-      </c>
-      <c r="B97" t="n">
-        <v>33.40954971313477</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>22.9187068939209</v>
-      </c>
-      <c r="B98" t="n">
-        <v>23.1744384765625</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>40</v>
-      </c>
-      <c r="B99" t="n">
-        <v>41.25974273681641</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>4.926108360290527</v>
-      </c>
-      <c r="B100" t="n">
-        <v>12.72627353668213</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>9.142857551574707</v>
-      </c>
-      <c r="B101" t="n">
-        <v>9.427213668823242</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>20.37218475341797</v>
-      </c>
-      <c r="B102" t="n">
-        <v>12.53428840637207</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>10.7737512588501</v>
-      </c>
-      <c r="B103" t="n">
-        <v>16.68436622619629</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>8.380952835083008</v>
-      </c>
-      <c r="B104" t="n">
-        <v>20.07804489135742</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>60</v>
-      </c>
-      <c r="B105" t="n">
-        <v>51.05000305175781</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>100</v>
-      </c>
-      <c r="B106" t="n">
-        <v>93.47613525390625</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>13.32027435302734</v>
-      </c>
-      <c r="B107" t="n">
-        <v>13.31569766998291</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>26.05288887023926</v>
-      </c>
-      <c r="B108" t="n">
-        <v>26.41663932800293</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>31.80952453613281</v>
-      </c>
-      <c r="B109" t="n">
-        <v>27.8096981048584</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>19.58863830566406</v>
-      </c>
-      <c r="B110" t="n">
-        <v>30.51956176757812</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B111" t="n">
-        <v>75.79036712646484</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>10.83743858337402</v>
-      </c>
-      <c r="B112" t="n">
-        <v>10.69191265106201</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>45.52381134033203</v>
-      </c>
-      <c r="B113" t="n">
-        <v>31.01309204101562</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>103.8000030517578</v>
-      </c>
-      <c r="B114" t="n">
-        <v>103.2940292358398</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>100</v>
-      </c>
-      <c r="B115" t="n">
-        <v>81.3668212890625</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>14.20176315307617</v>
-      </c>
-      <c r="B116" t="n">
-        <v>13.59575080871582</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>31</v>
-      </c>
-      <c r="B117" t="n">
-        <v>27.18924140930176</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>34.37805938720703</v>
-      </c>
-      <c r="B118" t="n">
-        <v>27.76696586608887</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>58.70000076293945</v>
-      </c>
-      <c r="B119" t="n">
-        <v>55.67111206054688</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>11.2380952835083</v>
-      </c>
-      <c r="B120" t="n">
-        <v>14.90440464019775</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>17.80952453613281</v>
-      </c>
-      <c r="B121" t="n">
-        <v>12.34929084777832</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>14.1304349899292</v>
-      </c>
-      <c r="B122" t="n">
-        <v>17.59025955200195</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>81</v>
-      </c>
-      <c r="B123" t="n">
-        <v>74.07945251464844</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>30.85210609436035</v>
-      </c>
-      <c r="B124" t="n">
-        <v>28.18710708618164</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>23.10000038146973</v>
-      </c>
-      <c r="B125" t="n">
-        <v>21.67893028259277</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>18.51126289367676</v>
-      </c>
-      <c r="B126" t="n">
-        <v>14.69366455078125</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>20.66601371765137</v>
-      </c>
-      <c r="B127" t="n">
-        <v>19.18043327331543</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>25.95494651794434</v>
-      </c>
-      <c r="B128" t="n">
-        <v>24.26495742797852</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>2.154750347137451</v>
-      </c>
-      <c r="B129" t="n">
-        <v>8.342830657958984</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>33.79999923706055</v>
-      </c>
-      <c r="B130" t="n">
-        <v>32.4688606262207</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>59.70000076293945</v>
-      </c>
-      <c r="B131" t="n">
-        <v>50.07796096801758</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>59.52381134033203</v>
-      </c>
-      <c r="B132" t="n">
-        <v>61.31392669677734</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>63.0476188659668</v>
-      </c>
-      <c r="B133" t="n">
-        <v>58.19982528686523</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>68.85713958740234</v>
-      </c>
-      <c r="B134" t="n">
-        <v>60.10115432739258</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>25.46523094177246</v>
-      </c>
-      <c r="B135" t="n">
-        <v>25.38484191894531</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>13.88888931274414</v>
-      </c>
-      <c r="B136" t="n">
-        <v>12.04385471343994</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>6.660137176513672</v>
-      </c>
-      <c r="B137" t="n">
-        <v>6.096660137176514</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>34.02777862548828</v>
-      </c>
-      <c r="B138" t="n">
-        <v>26.80062866210938</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>9.189723014831543</v>
-      </c>
-      <c r="B139" t="n">
-        <v>10.53780364990234</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>15.083251953125</v>
-      </c>
-      <c r="B140" t="n">
-        <v>14.68289947509766</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>58.76591491699219</v>
-      </c>
-      <c r="B141" t="n">
-        <v>58.16501998901367</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>27.79999923706055</v>
-      </c>
-      <c r="B142" t="n">
-        <v>18.82015037536621</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>14.1304349899292</v>
-      </c>
-      <c r="B143" t="n">
-        <v>17.59025955200195</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>6.502462863922119</v>
-      </c>
-      <c r="B144" t="n">
-        <v>5.498184204101562</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>1.665034294128418</v>
-      </c>
-      <c r="B145" t="n">
-        <v>8.007967948913574</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>20.27424049377441</v>
-      </c>
-      <c r="B146" t="n">
-        <v>15.91760540008545</v>
+        <v>23.57109260559082</v>
       </c>
     </row>
   </sheetData>
